--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487657_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487657_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.64</v>
+        <v>6.1832</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5101</v>
+        <v>6.2713</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1299</v>
+        <v>-0.0881</v>
       </c>
       <c r="G2" t="n">
         <v>2.3013</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8733</v>
+        <v>-0.33</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3325</v>
+        <v>-0.5712</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4592</v>
+        <v>0.2412</v>
       </c>
       <c r="V2" t="n">
         <v>1.8836</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.9335</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4924</v>
+        <v>1.0523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.366</v>
+        <v>-0.1188</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.128</v>
+        <v>-2.4759</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2861</v>
+        <v>-3.7049</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.4141</v>
+        <v>1.229</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9484</v>
+        <v>0.0965</v>
       </c>
       <c r="K3" t="n">
-        <v>2.278</v>
+        <v>-1.8166</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3296</v>
+        <v>1.9131</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0764</v>
+        <v>-2.5724</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.992</v>
+        <v>-1.8883</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0844</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7761</v>
+        <v>2.3284</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3582</v>
+        <v>-0.194</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1344</v>
+        <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9282</v>
+        <v>-0.1907</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6202</v>
+        <v>-0.3561</v>
       </c>
       <c r="U3" t="n">
-        <v>0.308</v>
+        <v>0.1655</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2821</v>
+        <v>1.2716</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4146</v>
+        <v>0.3278</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4517</v>
+        <v>0.1526</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.037</v>
+        <v>0.1752</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.4759</v>
+        <v>-1.128</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.7049</v>
+        <v>1.2861</v>
       </c>
       <c r="I4" t="n">
-        <v>1.229</v>
+        <v>-2.4141</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0965</v>
+        <v>0.9484</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.8166</v>
+        <v>2.278</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9131</v>
+        <v>-1.3296</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5724</v>
+        <v>-2.0764</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8883</v>
+        <v>-0.992</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.0844</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5224</v>
+        <v>2.1344</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7095</v>
+        <v>0.3976</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9567</v>
+        <v>0.2804</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2472</v>
+        <v>0.1172</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2716</v>
+        <v>0.2821</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>0.2821</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9997</v>
+        <v>-0.9325</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5071</v>
+        <v>-0.6266</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4925</v>
+        <v>-0.306</v>
       </c>
       <c r="G5" t="n">
-        <v>-5.8747</v>
+        <v>-0.884</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.5</v>
+        <v>-0.2167</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3747</v>
+        <v>-0.6673</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.8669</v>
+        <v>-0.6055</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9937</v>
+        <v>0.0618</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1268</v>
+        <v>-0.6673</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.0078</v>
+        <v>-0.2785</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.5062</v>
+        <v>-0.2785</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5015</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5224</v>
+        <v>0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6866</v>
+        <v>0.3881</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1429</v>
+        <v>-0.1545</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0762</v>
+        <v>-0.021</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2191</v>
+        <v>-0.1335</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4955</v>
+        <v>-0.2821</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0478</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0326</v>
+        <v>-1.0765</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7267</v>
+        <v>-0.8495</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.306</v>
+        <v>-0.2271</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.884</v>
+        <v>-0.2519</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2167</v>
+        <v>0.0206</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6673</v>
+        <v>-0.2725</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6055</v>
+        <v>0.0206</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0618</v>
+        <v>0.0206</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2785</v>
+        <v>-0.2725</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2785</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>-0.2725</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0.3881</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.3881</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.2546</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.1211</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.1335</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.2821</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1212</v>
+        <v>-1.1462</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5401</v>
+        <v>-1.9195</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4189</v>
+        <v>0.7733</v>
       </c>
       <c r="G7" t="n">
         <v>-2.4159</v>
@@ -1000,13 +1000,13 @@
         <v>3.4926</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7441</v>
+        <v>-0.7691</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.046</v>
+        <v>-0.4254</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.3437</v>
       </c>
       <c r="V7" t="n">
         <v>-0.0955</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2039</v>
+        <v>-1.3006</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9496</v>
+        <v>-1.0261</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2543</v>
+        <v>-0.2745</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2519</v>
+        <v>-5.8747</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0206</v>
+        <v>-4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2725</v>
+        <v>-1.3747</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0206</v>
+        <v>-1.8669</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0206</v>
+        <v>-1.9937</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.1268</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2725</v>
+        <v>-4.0078</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-2.5062</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2725</v>
+        <v>-1.5015</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9702</v>
+        <v>2.5224</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.6866</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0182</v>
+        <v>-0.4439</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.4428</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0182</v>
+        <v>-0.0011</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.4955</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8652</v>
+        <v>-2.0772</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0429</v>
+        <v>-0.789</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9081</v>
+        <v>-1.2882</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.0471</v>
+        <v>0.6021</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3462</v>
+        <v>0.6772</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.7009</v>
+        <v>-0.0751</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5054999999999999</v>
+        <v>3.1016</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9608</v>
+        <v>2.348</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4663</v>
+        <v>0.7536</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.5416</v>
+        <v>-2.4995</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.307</v>
+        <v>-1.6708</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2346</v>
+        <v>-0.8286</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1344</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1344</v>
+        <v>2.5224</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3297</v>
+        <v>-1.1151</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5484</v>
+        <v>-0.6503</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2187</v>
+        <v>-0.4649</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2821</v>
+        <v>-1.1761</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9441</v>
+        <v>-3.433</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4106</v>
+        <v>-0.7974</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5335</v>
+        <v>-2.6355</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6021</v>
+        <v>-5.0471</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6772</v>
+        <v>-1.3462</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0751</v>
+        <v>-3.7009</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1016</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>2.348</v>
+        <v>1.9608</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7536</v>
+        <v>-2.4663</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4995</v>
+        <v>-4.5416</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6708</v>
+        <v>-3.307</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8286</v>
+        <v>-1.2346</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3881</v>
+        <v>2.1344</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5224</v>
+        <v>2.1344</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9821</v>
+        <v>-0.2381</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2719</v>
+        <v>-0.2919</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7102000000000001</v>
+        <v>0.0538</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1761</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8462</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6869</v>
+        <v>-4.8685</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3883</v>
+        <v>-2.1065</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2987</v>
+        <v>-2.762</v>
       </c>
       <c r="G11" t="n">
         <v>-6.8176</v>
@@ -1312,13 +1312,13 @@
         <v>3.8806</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7216</v>
+        <v>-0.9032</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0891</v>
+        <v>-0.8073</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3675</v>
+        <v>-0.0959</v>
       </c>
       <c r="V11" t="n">
         <v>0.3299</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3206</v>
+        <v>-4.9626</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9016</v>
+        <v>-5.38</v>
       </c>
       <c r="F12" t="n">
-        <v>0.581</v>
+        <v>0.4174</v>
       </c>
       <c r="G12" t="n">
         <v>-6.5717</v>
@@ -1390,13 +1390,13 @@
         <v>3.1045</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8728</v>
+        <v>-0.5148</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1384</v>
+        <v>-0.6169</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2656</v>
+        <v>0.1021</v>
       </c>
       <c r="V12" t="n">
         <v>0.3776</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.2612</v>
+        <v>-12.3526</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9269</v>
+        <v>-6.018400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.334300000000001</v>
+        <v>-6.3343</v>
       </c>
       <c r="G13" t="n">
         <v>-28.5634</v>
@@ -1441,13 +1441,13 @@
         <v>-16.016</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2021999999999982</v>
+        <v>-0.202199999999999</v>
       </c>
       <c r="K13" t="n">
         <v>4.2184</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.420399999999999</v>
+        <v>-4.4204</v>
       </c>
       <c r="M13" t="n">
         <v>-28.3612</v>
@@ -1468,22 +1468,22 @@
         <v>26.1944</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.024799999999999</v>
+        <v>-4.1163</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.7109</v>
+        <v>-3.8024</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3139000000000003</v>
+        <v>-0.3139</v>
       </c>
       <c r="V13" t="n">
-        <v>4.804500000000001</v>
+        <v>4.8045</v>
       </c>
       <c r="W13" t="n">
-        <v>8.657999999999999</v>
+        <v>8.658000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.853599999999999</v>
+        <v>-3.8536</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7749</v>
+        <v>5.7091</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2826</v>
+        <v>3.0834</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4922</v>
+        <v>2.6257</v>
       </c>
       <c r="G14" t="n">
         <v>9.5564</v>
@@ -1546,13 +1546,13 @@
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1233</v>
+        <v>0.8109</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9567</v>
+        <v>-0.1559</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8334</v>
+        <v>0.9669</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5537</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2839</v>
+        <v>5.103</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6881</v>
+        <v>1.589</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5958</v>
+        <v>3.514</v>
       </c>
       <c r="G15" t="n">
         <v>7.3973</v>
@@ -1624,13 +1624,13 @@
         <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3314</v>
+        <v>1.1505</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8479</v>
+        <v>0.053</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1793</v>
+        <v>1.0975</v>
       </c>
       <c r="V15" t="n">
         <v>0.0478</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3112</v>
+        <v>2.8835</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6324</v>
+        <v>1.232</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6787</v>
+        <v>1.6515</v>
       </c>
       <c r="G16" t="n">
         <v>2.4511</v>
@@ -1702,13 +1702,13 @@
         <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6541</v>
+        <v>1.2265</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6684</v>
+        <v>0.268</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9857</v>
+        <v>0.9584</v>
       </c>
       <c r="V16" t="n">
         <v>0.5642</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4203</v>
+        <v>1.9058</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4757</v>
+        <v>0.9166</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0554</v>
+        <v>0.9892</v>
       </c>
       <c r="G17" t="n">
-        <v>2.805</v>
+        <v>1.488</v>
       </c>
       <c r="H17" t="n">
-        <v>0.664</v>
+        <v>1.3651</v>
       </c>
       <c r="I17" t="n">
-        <v>2.141</v>
+        <v>0.1229</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5691</v>
+        <v>1.9855</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9886</v>
+        <v>1.7013</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5804</v>
+        <v>0.2842</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.764</v>
+        <v>-0.4975</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3246</v>
+        <v>-0.3362</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4394</v>
+        <v>-0.1613</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>2.469</v>
+        <v>-0.0583</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1366</v>
+        <v>-0.1868</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3325</v>
+        <v>0.1285</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8836</v>
+        <v>0.2821</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0955</v>
+        <v>0.2821</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0543</v>
+        <v>1.5824</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1168</v>
+        <v>2.1744</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9375</v>
+        <v>-0.5921</v>
       </c>
       <c r="G18" t="n">
-        <v>1.488</v>
+        <v>2.805</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3651</v>
+        <v>0.664</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1229</v>
+        <v>2.141</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9855</v>
+        <v>3.5691</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7013</v>
+        <v>0.9886</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2842</v>
+        <v>2.5804</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4975</v>
+        <v>-0.764</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3362</v>
+        <v>-0.3246</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1613</v>
+        <v>-0.4394</v>
       </c>
       <c r="P18" t="n">
-        <v>0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0902</v>
+        <v>1.631</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0134</v>
+        <v>0.8353</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.7958</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2821</v>
+        <v>-1.8836</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>-0.0955</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9263</v>
+        <v>0.9601</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2669</v>
+        <v>-0.0667</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1931</v>
+        <v>1.0268</v>
       </c>
       <c r="G19" t="n">
         <v>5.8149</v>
@@ -1936,13 +1936,13 @@
         <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1562</v>
+        <v>1.19</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0471</v>
+        <v>0.1531</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2033</v>
+        <v>1.0369</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6119</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3878</v>
+        <v>0.7516</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2198</v>
+        <v>1.42</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8319</v>
+        <v>-0.6684</v>
       </c>
       <c r="G20" t="n">
         <v>1.7128</v>
@@ -2014,13 +2014,13 @@
         <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2667</v>
+        <v>0.097</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2423</v>
+        <v>-0.0421</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0244</v>
+        <v>0.1391</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1825</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>-0.5971</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5854</v>
+        <v>-0.3974</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2061</v>
@@ -2092,13 +2092,13 @@
         <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5704</v>
+        <v>-0.3824</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4116</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1588</v>
+        <v>0.0292</v>
       </c>
       <c r="V21" t="n">
         <v>1.1761</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.631</v>
+        <v>-1.9614</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8601</v>
+        <v>-1.1604</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7709</v>
+        <v>-0.801</v>
       </c>
       <c r="G22" t="n">
         <v>0.4033</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3149</v>
+        <v>-0.0154</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1828</v>
+        <v>-0.1175</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1321</v>
+        <v>0.1021</v>
       </c>
       <c r="V22" t="n">
         <v>-2.5433</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.084</v>
+        <v>-2.0112</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3571</v>
+        <v>-2.257</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2731</v>
+        <v>0.2459</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8595</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0305</v>
+        <v>0.0423</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1512</v>
+        <v>0.1239</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13.2612</v>
+        <v>13.9284</v>
       </c>
       <c r="E24" t="n">
-        <v>6.334200000000002</v>
+        <v>6.334200000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>6.926800000000001</v>
+        <v>7.5942</v>
       </c>
       <c r="G24" t="n">
         <v>28.5632</v>
@@ -2326,13 +2326,13 @@
         <v>10.6719</v>
       </c>
       <c r="S24" t="n">
-        <v>5.0249</v>
+        <v>5.6921</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3139000000000002</v>
+        <v>0.3139000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>4.711100000000001</v>
+        <v>5.3783</v>
       </c>
       <c r="V24" t="n">
         <v>-4.804399999999999</v>
